--- a/VERGARA/Octubre/vergara Octubre.xlsx
+++ b/VERGARA/Octubre/vergara Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A64602A-6664-41A3-9D0E-73E15884E485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1A3EB0-ACA9-4028-A9C3-647423631D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$Q$105</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$102</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$103</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="281">
   <si>
     <t>MAIL: consorciovergara1670@gmail.com</t>
   </si>
@@ -869,6 +869,9 @@
   </si>
   <si>
     <t>Deposito no identificado Flores Mattar Jose 13/10</t>
+  </si>
+  <si>
+    <t>Edesur - cliente nro. 01469567 - Mes anterior</t>
   </si>
 </sst>
 </file>
@@ -1934,84 +1937,40 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2062,7 +2021,51 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2423,21 +2426,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M106"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M107"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="63" t="s">
         <v>0</v>
@@ -2446,7 +2449,7 @@
       <c r="D1" s="63"/>
       <c r="E1" s="64"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="123" t="s">
         <v>1</v>
@@ -2455,7 +2458,7 @@
       <c r="D2" s="123"/>
       <c r="E2" s="65"/>
     </row>
-    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
       <c r="B3" s="124" t="s">
         <v>2</v>
@@ -2466,7 +2469,7 @@
       </c>
       <c r="E3" s="65"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -2477,18 +2480,18 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="203" t="s">
+      <c r="B5" s="214" t="s">
         <v>254</v>
       </c>
-      <c r="C5" s="204"/>
-      <c r="D5" s="204"/>
-      <c r="E5" s="205"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="210"/>
+      <c r="D5" s="210"/>
+      <c r="E5" s="211"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -2499,57 +2502,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="206" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="215" t="s">
         <v>253</v>
       </c>
-      <c r="C8" s="207"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="207"/>
-      <c r="C9" s="207"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="207"/>
-      <c r="C10" s="207"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="208" t="s">
+      <c r="C8" s="205"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="216" t="s">
         <v>248</v>
       </c>
-      <c r="B13" s="209"/>
-      <c r="C13" s="209"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="209"/>
-      <c r="B14" s="209"/>
-      <c r="C14" s="209"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="209"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="209"/>
-      <c r="B15" s="209"/>
-      <c r="C15" s="209"/>
-      <c r="D15" s="209"/>
-      <c r="E15" s="209"/>
-    </row>
-    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="209"/>
-      <c r="B16" s="209"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="209"/>
-      <c r="E16" s="209"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="217"/>
+      <c r="C13" s="217"/>
+      <c r="D13" s="217"/>
+      <c r="E13" s="217"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="217"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
+      <c r="D14" s="217"/>
+      <c r="E14" s="217"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="217"/>
+      <c r="B15" s="217"/>
+      <c r="C15" s="217"/>
+      <c r="D15" s="217"/>
+      <c r="E15" s="217"/>
+    </row>
+    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="217"/>
+      <c r="B16" s="217"/>
+      <c r="C16" s="217"/>
+      <c r="D16" s="217"/>
+      <c r="E16" s="217"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2558,7 +2561,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
         <v>10</v>
       </c>
@@ -2567,7 +2570,7 @@
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>11</v>
       </c>
@@ -2578,7 +2581,7 @@
       </c>
       <c r="E22" s="82"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
@@ -2590,7 +2593,7 @@
       <c r="E23" s="82"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>13</v>
       </c>
@@ -2602,7 +2605,7 @@
       <c r="E24" s="82"/>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="55" t="s">
         <v>14</v>
       </c>
@@ -2615,7 +2618,7 @@
       <c r="E25" s="83"/>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="52"/>
       <c r="B26" s="158"/>
       <c r="C26" s="158"/>
@@ -2623,7 +2626,7 @@
       <c r="E26" s="159"/>
       <c r="G26" s="19"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="55" t="s">
         <v>14</v>
       </c>
@@ -2636,7 +2639,7 @@
       <c r="E27" s="83"/>
       <c r="G27" s="19"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="51" t="s">
         <v>15</v>
       </c>
@@ -2649,7 +2652,7 @@
       </c>
       <c r="F28" s="19"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="32" t="s">
         <v>16</v>
       </c>
@@ -2658,11 +2661,11 @@
       <c r="D29" s="33"/>
       <c r="E29" s="85"/>
     </row>
-    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="210" t="s">
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="206" t="s">
         <v>255</v>
       </c>
-      <c r="B30" s="211"/>
+      <c r="B30" s="207"/>
       <c r="C30" s="5"/>
       <c r="D30" s="178">
         <v>40000</v>
@@ -2671,11 +2674,11 @@
         <v>267</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="210" t="s">
+    <row r="31" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="206" t="s">
         <v>257</v>
       </c>
-      <c r="B31" s="211"/>
+      <c r="B31" s="207"/>
       <c r="C31" s="5"/>
       <c r="D31" s="178">
         <f>470000</f>
@@ -2685,7 +2688,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="25" t="s">
         <v>17</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="30" t="s">
         <v>18</v>
       </c>
@@ -2706,7 +2709,7 @@
       <c r="D33" s="34"/>
       <c r="E33" s="62"/>
     </row>
-    <row r="34" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="136" t="s">
         <v>19</v>
       </c>
@@ -2720,18 +2723,18 @@
       </c>
       <c r="G34" s="135"/>
     </row>
-    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="210" t="s">
+    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="206" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="211"/>
+      <c r="B35" s="207"/>
       <c r="C35" s="53"/>
       <c r="D35" s="180">
         <v>719.9</v>
       </c>
       <c r="E35" s="108"/>
     </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="25" t="s">
         <v>21</v>
       </c>
@@ -2743,7 +2746,7 @@
         <v>71587.899999999994</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
         <v>22</v>
       </c>
@@ -2752,7 +2755,7 @@
       <c r="D37" s="37"/>
       <c r="E37" s="88"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>23</v>
       </c>
@@ -2766,7 +2769,7 @@
       </c>
       <c r="G38" s="114"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>256</v>
       </c>
@@ -2781,7 +2784,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="str">
         <f>A39</f>
         <v>Sindicatos mes de OCTUBRE</v>
@@ -2798,7 +2801,7 @@
         <v>Debito 14/10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="str">
         <f>A40</f>
         <v>Sindicatos mes de OCTUBRE</v>
@@ -2815,7 +2818,7 @@
         <v>Debito 14/10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="25" t="s">
         <v>27</v>
       </c>
@@ -2827,7 +2830,7 @@
         <v>442486.67</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
         <v>28</v>
       </c>
@@ -2836,7 +2839,7 @@
       <c r="D43" s="37"/>
       <c r="E43" s="88"/>
     </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>29</v>
       </c>
@@ -2849,7 +2852,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>30</v>
       </c>
@@ -2862,11 +2865,11 @@
         <v>264</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="210" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="206" t="s">
         <v>31</v>
       </c>
-      <c r="B46" s="211"/>
+      <c r="B46" s="207"/>
       <c r="C46" s="5"/>
       <c r="D46" s="180">
         <v>94467.63</v>
@@ -2875,7 +2878,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="25" t="s">
         <v>32</v>
       </c>
@@ -2887,7 +2890,7 @@
         <v>2010748.21</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="32" t="s">
         <v>33</v>
       </c>
@@ -2896,11 +2899,11 @@
       <c r="D48" s="36"/>
       <c r="E48" s="90"/>
     </row>
-    <row r="49" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="215" t="s">
+    <row r="49" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="212" t="s">
         <v>266</v>
       </c>
-      <c r="B49" s="216"/>
+      <c r="B49" s="213"/>
       <c r="C49" s="54"/>
       <c r="D49" s="180">
         <v>300000</v>
@@ -2910,7 +2913,7 @@
       </c>
       <c r="H49" s="114"/>
     </row>
-    <row r="50" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="160" t="s">
         <v>277</v>
       </c>
@@ -2924,7 +2927,7 @@
       </c>
       <c r="H50" s="114"/>
     </row>
-    <row r="51" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="91" t="s">
         <v>275</v>
       </c>
@@ -2938,7 +2941,7 @@
       </c>
       <c r="H51" s="114"/>
     </row>
-    <row r="52" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="160" t="s">
         <v>252</v>
       </c>
@@ -2952,11 +2955,11 @@
       </c>
       <c r="H52" s="114"/>
     </row>
-    <row r="53" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="215" t="s">
+    <row r="53" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="212" t="s">
         <v>261</v>
       </c>
-      <c r="B53" s="216"/>
+      <c r="B53" s="213"/>
       <c r="C53" s="54"/>
       <c r="D53" s="180">
         <v>45000</v>
@@ -2966,11 +2969,11 @@
       </c>
       <c r="H53" s="114"/>
     </row>
-    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="215" t="s">
+    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="212" t="s">
         <v>269</v>
       </c>
-      <c r="B54" s="216"/>
+      <c r="B54" s="213"/>
       <c r="C54" s="54"/>
       <c r="D54" s="180">
         <v>75000</v>
@@ -2980,7 +2983,7 @@
       </c>
       <c r="H54" s="114"/>
     </row>
-    <row r="55" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="160" t="s">
         <v>272</v>
       </c>
@@ -2994,7 +2997,7 @@
       </c>
       <c r="H55" s="114"/>
     </row>
-    <row r="56" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="160" t="s">
         <v>274</v>
       </c>
@@ -3008,21 +3011,21 @@
       </c>
       <c r="H56" s="114"/>
     </row>
-    <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="160" t="s">
         <v>271</v>
       </c>
       <c r="B57" s="161"/>
       <c r="C57" s="54"/>
       <c r="D57" s="180">
-        <v>123000</v>
+        <v>120000</v>
       </c>
       <c r="E57" s="157" t="s">
         <v>270</v>
       </c>
       <c r="H57" s="114"/>
     </row>
-    <row r="58" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="25" t="s">
         <v>34</v>
       </c>
@@ -3031,10 +3034,10 @@
       <c r="D58" s="30"/>
       <c r="E58" s="162">
         <f>SUM(D49:D57)</f>
-        <v>1348855.83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1345855.83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="32" t="s">
         <v>35</v>
       </c>
@@ -3043,7 +3046,7 @@
       <c r="D59" s="27"/>
       <c r="E59" s="90"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>36</v>
       </c>
@@ -3054,7 +3057,7 @@
       </c>
       <c r="E60" s="98"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>37</v>
       </c>
@@ -3065,7 +3068,7 @@
       </c>
       <c r="E61" s="95"/>
     </row>
-    <row r="62" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="51" t="s">
         <v>17</v>
       </c>
@@ -3077,14 +3080,14 @@
         <v>208699.63</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="82"/>
       <c r="E63" s="100"/>
     </row>
-    <row r="64" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="28" t="s">
         <v>38</v>
       </c>
@@ -3093,14 +3096,14 @@
       <c r="D64" s="101"/>
       <c r="E64" s="128"/>
     </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="D65" s="102"/>
       <c r="E65" s="103"/>
       <c r="F65" s="44"/>
       <c r="G65" s="130"/>
     </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>39</v>
       </c>
@@ -3109,19 +3112,19 @@
       <c r="D66" s="104"/>
       <c r="E66" s="174">
         <f>(SUM(E28:E64))</f>
-        <v>5146141.2399999993</v>
+        <v>5143141.2399999993</v>
       </c>
       <c r="F66" s="127"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D67" s="102"/>
       <c r="E67" s="102"/>
     </row>
-    <row r="68" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D68" s="102"/>
       <c r="E68" s="102"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>40</v>
       </c>
@@ -3130,21 +3133,21 @@
       <c r="D69" s="105"/>
       <c r="E69" s="106"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="210"/>
-      <c r="B70" s="211"/>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="206"/>
+      <c r="B70" s="207"/>
       <c r="C70" s="5"/>
       <c r="D70" s="92"/>
       <c r="E70" s="89"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="91"/>
       <c r="B71" s="93"/>
       <c r="C71" s="5"/>
       <c r="D71" s="92"/>
       <c r="E71" s="89"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="49"/>
       <c r="B72" s="48"/>
       <c r="C72" s="48"/>
@@ -3154,19 +3157,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="214" t="s">
+    <row r="73" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="209" t="s">
         <v>41</v>
       </c>
-      <c r="B75" s="204"/>
-      <c r="C75" s="204"/>
-      <c r="D75" s="205"/>
+      <c r="B75" s="210"/>
+      <c r="C75" s="210"/>
+      <c r="D75" s="211"/>
       <c r="E75" s="131"/>
     </row>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>42</v>
       </c>
@@ -3178,26 +3181,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="79" t="s">
         <v>43</v>
       </c>
       <c r="B79" s="80">
         <f>E66</f>
-        <v>5146141.2399999993</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5143141.2399999993</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="79" t="s">
         <v>44</v>
       </c>
       <c r="B80" s="80">
         <f>E66-E64</f>
-        <v>5146141.2399999993</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5143141.2399999993</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="79" t="s">
         <v>45</v>
       </c>
@@ -3206,7 +3209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="79" t="s">
         <v>46</v>
       </c>
@@ -3215,15 +3218,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="45" t="s">
         <v>47</v>
       </c>
       <c r="B84" s="115"/>
       <c r="C84" s="20"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="29" t="s">
         <v>48</v>
       </c>
@@ -3232,7 +3235,7 @@
       </c>
       <c r="C85" s="22"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="21" t="s">
         <v>49</v>
       </c>
@@ -3242,17 +3245,17 @@
       </c>
       <c r="C86" s="20"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="21" t="s">
         <v>50</v>
       </c>
       <c r="B87" s="95">
-        <f>B101</f>
+        <f>B102</f>
         <v>269200</v>
       </c>
       <c r="C87" s="20"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="111" t="s">
         <v>51</v>
       </c>
@@ -3261,17 +3264,17 @@
       </c>
       <c r="C88" s="20"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="40" t="s">
         <v>52</v>
       </c>
       <c r="B89" s="47">
         <f>-B80</f>
-        <v>-5146141.2399999993</v>
+        <v>-5143141.2399999993</v>
       </c>
       <c r="C89" s="20"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="40" t="s">
         <v>53</v>
       </c>
@@ -3281,144 +3284,153 @@
       </c>
       <c r="C90" s="20"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="B91" s="47">
+        <v>-1925904.9</v>
+      </c>
+      <c r="C91" s="20"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B91" s="47">
+      <c r="B92" s="47">
         <f>-PRORRATEO!F2</f>
         <v>-1814660.39</v>
       </c>
-      <c r="C91" s="20"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="24" t="s">
+      <c r="C92" s="20"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B92" s="47">
+      <c r="B93" s="47">
         <f>-(B81)</f>
         <v>0</v>
       </c>
-      <c r="C92" s="20"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="118" t="s">
+      <c r="C93" s="20"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="B93" s="119">
-        <f>SUM(B85:B92)</f>
-        <v>453165.01400000579</v>
-      </c>
-      <c r="C93" s="23"/>
-      <c r="D93" s="44"/>
-      <c r="E93" s="253"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B94" s="42"/>
+      <c r="B94" s="119">
+        <f>SUM(B85:B93)</f>
+        <v>-1469739.8859999941</v>
+      </c>
       <c r="C94" s="23"/>
       <c r="D94" s="44"/>
-      <c r="E94" s="116"/>
-      <c r="F94" s="117"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E94" s="203"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B95" s="42"/>
       <c r="C95" s="23"/>
       <c r="D95" s="44"/>
       <c r="E95" s="116"/>
       <c r="F95" s="117"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="213" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B96" s="42"/>
+      <c r="C96" s="23"/>
+      <c r="D96" s="44"/>
+      <c r="E96" s="116"/>
+      <c r="F96" s="117"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A97" s="208" t="s">
         <v>56</v>
       </c>
-      <c r="B96" s="207"/>
-      <c r="C96" s="207"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A97" s="207"/>
-      <c r="B97" s="207"/>
-      <c r="C97" s="207"/>
-    </row>
-    <row r="98" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="53" t="s">
+      <c r="B97" s="205"/>
+      <c r="C97" s="205"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="205"/>
+      <c r="B98" s="205"/>
+      <c r="C98" s="205"/>
+    </row>
+    <row r="99" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="53" t="s">
         <v>279</v>
       </c>
-      <c r="B98" s="181">
+      <c r="B99" s="181">
         <v>269200</v>
       </c>
-      <c r="C98" s="35">
+      <c r="C99" s="35">
         <v>11948.17</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="53"/>
-      <c r="B99" s="35"/>
-      <c r="C99" s="35"/>
-    </row>
-    <row r="100" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="121"/>
+    <row r="100" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="53"/>
       <c r="B100" s="35"/>
-      <c r="C100" s="35">
+      <c r="C100" s="35"/>
+    </row>
+    <row r="101" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="121"/>
+      <c r="B101" s="35"/>
+      <c r="C101" s="35">
         <v>61209</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="45" t="s">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="B101" s="107">
-        <f>SUM(B98:B100)</f>
+      <c r="B102" s="107">
+        <f>SUM(B99:B101)</f>
         <v>269200</v>
       </c>
-      <c r="C101" s="46"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M102" s="7"/>
-    </row>
-    <row r="103" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="212"/>
-      <c r="B103" s="207"/>
-      <c r="C103" s="207"/>
-      <c r="D103" s="207"/>
-      <c r="E103" s="207"/>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="207"/>
-      <c r="B104" s="207"/>
-      <c r="C104" s="207"/>
-      <c r="D104" s="207"/>
-      <c r="E104" s="207"/>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A105" s="207"/>
-      <c r="B105" s="207"/>
-      <c r="C105" s="207"/>
-      <c r="D105" s="207"/>
-      <c r="E105" s="207"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A106" s="207"/>
-      <c r="B106" s="207"/>
-      <c r="C106" s="207"/>
-      <c r="D106" s="207"/>
-      <c r="E106" s="207"/>
+      <c r="C102" s="46"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M103" s="7"/>
+    </row>
+    <row r="104" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="204"/>
+      <c r="B104" s="205"/>
+      <c r="C104" s="205"/>
+      <c r="D104" s="205"/>
+      <c r="E104" s="205"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A105" s="205"/>
+      <c r="B105" s="205"/>
+      <c r="C105" s="205"/>
+      <c r="D105" s="205"/>
+      <c r="E105" s="205"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A106" s="205"/>
+      <c r="B106" s="205"/>
+      <c r="C106" s="205"/>
+      <c r="D106" s="205"/>
+      <c r="E106" s="205"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A107" s="205"/>
+      <c r="B107" s="205"/>
+      <c r="C107" s="205"/>
+      <c r="D107" s="205"/>
+      <c r="E107" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A103:E106"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A104:E107"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A96:C97"/>
+    <mergeCell ref="A97:C98"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A75:D75"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A54:B54"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3429,61 +3441,61 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T104"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="11.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" customWidth="1"/>
-    <col min="18" max="18" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="11" width="9.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="11.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" customWidth="1"/>
+    <col min="17" max="17" width="14.33203125" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="245"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="247"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="229"/>
       <c r="E1" s="187" t="s">
         <v>260</v>
       </c>
-      <c r="F1" s="251">
+      <c r="F1" s="233">
         <v>1864064.43</v>
       </c>
-      <c r="G1" s="250"/>
-      <c r="H1" s="236"/>
-      <c r="I1" s="237"/>
-      <c r="J1" s="238"/>
+      <c r="G1" s="232"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="220"/>
       <c r="K1" s="189" t="s">
         <v>57</v>
       </c>
       <c r="L1" s="188"/>
-      <c r="M1" s="249">
+      <c r="M1" s="231">
         <f>S1</f>
-        <v>5146141.2399999993</v>
-      </c>
-      <c r="N1" s="250"/>
-      <c r="O1" s="239">
+        <v>5143141.2399999993</v>
+      </c>
+      <c r="N1" s="232"/>
+      <c r="O1" s="221">
         <v>3600000</v>
       </c>
-      <c r="P1" s="240"/>
-      <c r="Q1" s="241"/>
+      <c r="P1" s="222"/>
+      <c r="Q1" s="223"/>
       <c r="R1" s="19"/>
       <c r="S1">
-        <v>5146141.2399999993</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5143141.2399999993</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
       <c r="B2" s="190"/>
       <c r="C2" s="193"/>
@@ -3491,101 +3503,101 @@
       <c r="E2" s="191" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="228">
+      <c r="F2" s="236">
         <v>1814660.39</v>
       </c>
-      <c r="G2" s="229"/>
-      <c r="H2" s="233"/>
-      <c r="I2" s="234"/>
-      <c r="J2" s="235"/>
+      <c r="G2" s="237"/>
+      <c r="H2" s="244"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="246"/>
       <c r="K2" s="192" t="s">
         <v>59</v>
       </c>
       <c r="L2" s="192"/>
-      <c r="M2" s="232"/>
-      <c r="N2" s="229"/>
-      <c r="O2" s="242">
+      <c r="M2" s="243"/>
+      <c r="N2" s="237"/>
+      <c r="O2" s="224">
         <v>48523.32</v>
       </c>
-      <c r="P2" s="243"/>
-      <c r="Q2" s="244"/>
-    </row>
-    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="217" t="s">
+      <c r="P2" s="225"/>
+      <c r="Q2" s="226"/>
+    </row>
+    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="247" t="s">
         <v>60</v>
       </c>
       <c r="B3" s="112"/>
-      <c r="C3" s="224" t="s">
+      <c r="C3" s="238" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="224" t="s">
+      <c r="D3" s="238" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="231" t="s">
+      <c r="E3" s="242" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="226" t="s">
+      <c r="F3" s="252" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="219" t="s">
+      <c r="G3" s="249" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="224" t="s">
+      <c r="H3" s="238" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="223" t="s">
+      <c r="I3" s="251" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="221" t="s">
+      <c r="J3" s="239" t="s">
         <v>67</v>
       </c>
-      <c r="K3" s="230" t="str">
+      <c r="K3" s="241" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="221" t="s">
+      <c r="L3" s="239" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="221" t="s">
+      <c r="M3" s="239" t="s">
         <v>69</v>
       </c>
-      <c r="N3" s="221" t="s">
+      <c r="N3" s="239" t="s">
         <v>70</v>
       </c>
-      <c r="O3" s="221" t="s">
+      <c r="O3" s="239" t="s">
         <v>71</v>
       </c>
       <c r="P3" s="186" t="s">
         <v>72</v>
       </c>
-      <c r="Q3" s="252" t="s">
+      <c r="Q3" s="234" t="s">
         <v>73</v>
       </c>
       <c r="T3" s="44"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="218"/>
+    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="248"/>
       <c r="B4" s="112"/>
-      <c r="C4" s="225"/>
-      <c r="D4" s="225"/>
-      <c r="E4" s="222"/>
-      <c r="F4" s="227"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="225"/>
-      <c r="I4" s="222"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="225"/>
-      <c r="L4" s="222"/>
-      <c r="M4" s="222"/>
-      <c r="N4" s="222"/>
-      <c r="O4" s="222"/>
+      <c r="C4" s="235"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="240"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="250"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="240"/>
+      <c r="J4" s="240"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="240"/>
+      <c r="M4" s="240"/>
+      <c r="N4" s="240"/>
+      <c r="O4" s="240"/>
       <c r="P4" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 14/11</v>
       </c>
-      <c r="Q4" s="225"/>
-    </row>
-    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="235"/>
+    </row>
+    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="60"/>
       <c r="B5" s="60" t="s">
         <v>74</v>
@@ -3618,7 +3630,7 @@
       </c>
       <c r="L5" s="69">
         <f t="shared" ref="L5:L36" si="3">M$1*F5</f>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M5" s="120">
         <f t="shared" ref="M5:M36" si="4">F$1*F5</f>
@@ -3634,18 +3646,18 @@
       </c>
       <c r="P5" s="70">
         <f t="shared" ref="P5:P36" si="7">ROUND(SUM(I5:O5),0) + R5</f>
-        <v>354565.33</v>
+        <v>354504.33</v>
       </c>
       <c r="Q5" s="71">
         <f t="shared" ref="Q5:Q36" si="8">ROUND(P5*3%,0) + P5</f>
-        <v>365202.33</v>
+        <v>365139.33</v>
       </c>
       <c r="R5" s="44">
         <f t="shared" ref="R5:R36" si="9">ROUND(0.001+C5/100,2)</f>
         <v>0.33</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="59"/>
       <c r="B6" s="59" t="s">
         <v>76</v>
@@ -3681,7 +3693,7 @@
       </c>
       <c r="L6" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M6" s="183">
         <f t="shared" si="4"/>
@@ -3697,11 +3709,11 @@
       </c>
       <c r="P6" s="184">
         <f t="shared" si="7"/>
-        <v>122666.34</v>
+        <v>122624.34</v>
       </c>
       <c r="Q6" s="185">
         <f t="shared" si="8"/>
-        <v>126346.34</v>
+        <v>126303.34</v>
       </c>
       <c r="R6" s="44">
         <f t="shared" si="9"/>
@@ -3709,7 +3721,7 @@
       </c>
       <c r="S6" s="44"/>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="59">
         <v>1</v>
       </c>
@@ -3747,7 +3759,7 @@
       </c>
       <c r="L7" s="182">
         <f t="shared" si="3"/>
-        <v>73075.205607999989</v>
+        <v>73032.605607999998</v>
       </c>
       <c r="M7" s="183">
         <f t="shared" si="4"/>
@@ -3763,18 +3775,18 @@
       </c>
       <c r="P7" s="184">
         <f t="shared" si="7"/>
-        <v>125313.35</v>
+        <v>125270.35</v>
       </c>
       <c r="Q7" s="185">
         <f t="shared" si="8"/>
-        <v>129072.35</v>
+        <v>129028.35</v>
       </c>
       <c r="R7" s="44">
         <f t="shared" si="9"/>
         <v>0.35</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="59">
         <v>2</v>
       </c>
@@ -3812,7 +3824,7 @@
       </c>
       <c r="L8" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M8" s="183">
         <f t="shared" si="4"/>
@@ -3828,11 +3840,11 @@
       </c>
       <c r="P8" s="184">
         <f t="shared" si="7"/>
-        <v>173215.35999999999</v>
+        <v>173155.36</v>
       </c>
       <c r="Q8" s="185">
         <f t="shared" si="8"/>
-        <v>178411.36</v>
+        <v>178350.36</v>
       </c>
       <c r="R8" s="44">
         <f t="shared" si="9"/>
@@ -3840,7 +3852,7 @@
       </c>
       <c r="T8" s="44"/>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="59">
         <v>3</v>
       </c>
@@ -3880,7 +3892,7 @@
       </c>
       <c r="L9" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M9" s="183">
         <f t="shared" si="4"/>
@@ -3896,11 +3908,11 @@
       </c>
       <c r="P9" s="184">
         <f t="shared" si="7"/>
-        <v>178262.37</v>
+        <v>178202.37</v>
       </c>
       <c r="Q9" s="185">
         <f t="shared" si="8"/>
-        <v>183610.37</v>
+        <v>183548.37</v>
       </c>
       <c r="R9" s="44">
         <f t="shared" si="9"/>
@@ -3908,7 +3920,7 @@
       </c>
       <c r="T9" s="44"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="59">
         <v>4</v>
       </c>
@@ -3948,7 +3960,7 @@
       </c>
       <c r="L10" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M10" s="183">
         <f t="shared" si="4"/>
@@ -3964,18 +3976,18 @@
       </c>
       <c r="P10" s="184">
         <f t="shared" si="7"/>
-        <v>94865.38</v>
+        <v>94824.38</v>
       </c>
       <c r="Q10" s="185">
         <f t="shared" si="8"/>
-        <v>97711.38</v>
+        <v>97669.38</v>
       </c>
       <c r="R10" s="44">
         <f t="shared" si="9"/>
         <v>0.38</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="59">
         <v>5</v>
       </c>
@@ -4013,7 +4025,7 @@
       </c>
       <c r="L11" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M11" s="183">
         <f t="shared" si="4"/>
@@ -4029,18 +4041,18 @@
       </c>
       <c r="P11" s="184">
         <f t="shared" si="7"/>
-        <v>122666.39</v>
+        <v>122624.39</v>
       </c>
       <c r="Q11" s="185">
         <f t="shared" si="8"/>
-        <v>126346.39</v>
+        <v>126303.39</v>
       </c>
       <c r="R11" s="44">
         <f t="shared" si="9"/>
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="59">
         <v>6</v>
       </c>
@@ -4078,7 +4090,7 @@
       </c>
       <c r="L12" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M12" s="183">
         <f t="shared" si="4"/>
@@ -4094,18 +4106,18 @@
       </c>
       <c r="P12" s="184">
         <f t="shared" si="7"/>
-        <v>171127.4</v>
+        <v>171067.4</v>
       </c>
       <c r="Q12" s="185">
         <f t="shared" si="8"/>
-        <v>176261.4</v>
+        <v>176199.4</v>
       </c>
       <c r="R12" s="44">
         <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="59">
         <v>7</v>
       </c>
@@ -4144,7 +4156,7 @@
       </c>
       <c r="L13" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M13" s="183">
         <f t="shared" si="4"/>
@@ -4160,18 +4172,18 @@
       </c>
       <c r="P13" s="184">
         <f t="shared" si="7"/>
-        <v>465626.41</v>
+        <v>465566.41</v>
       </c>
       <c r="Q13" s="185">
         <f t="shared" si="8"/>
-        <v>479595.41</v>
+        <v>479533.41</v>
       </c>
       <c r="R13" s="44">
         <f t="shared" si="9"/>
         <v>0.41</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="59">
         <v>8</v>
       </c>
@@ -4211,7 +4223,7 @@
       </c>
       <c r="L14" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M14" s="183">
         <f t="shared" si="4"/>
@@ -4227,18 +4239,18 @@
       </c>
       <c r="P14" s="184">
         <f t="shared" si="7"/>
-        <v>122666.42</v>
+        <v>122624.42</v>
       </c>
       <c r="Q14" s="185">
         <f t="shared" si="8"/>
-        <v>126346.42</v>
+        <v>126303.42</v>
       </c>
       <c r="R14" s="44">
         <f t="shared" si="9"/>
         <v>0.42</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="59">
         <v>1</v>
       </c>
@@ -4278,7 +4290,7 @@
       </c>
       <c r="L15" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M15" s="183">
         <f t="shared" si="4"/>
@@ -4294,18 +4306,18 @@
       </c>
       <c r="P15" s="184">
         <f t="shared" si="7"/>
-        <v>122666.43</v>
+        <v>122624.43</v>
       </c>
       <c r="Q15" s="185">
         <f t="shared" si="8"/>
-        <v>126346.43</v>
+        <v>126303.43</v>
       </c>
       <c r="R15" s="44">
         <f t="shared" si="9"/>
         <v>0.43</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="59">
         <v>1</v>
       </c>
@@ -4344,7 +4356,7 @@
       </c>
       <c r="L16" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M16" s="183">
         <f t="shared" si="4"/>
@@ -4360,18 +4372,18 @@
       </c>
       <c r="P16" s="184">
         <f t="shared" si="7"/>
-        <v>173127.44</v>
+        <v>173067.44</v>
       </c>
       <c r="Q16" s="185">
         <f t="shared" si="8"/>
-        <v>178321.44</v>
+        <v>178259.44</v>
       </c>
       <c r="R16" s="44">
         <f t="shared" si="9"/>
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="59">
         <v>2</v>
       </c>
@@ -4411,7 +4423,7 @@
       </c>
       <c r="L17" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M17" s="183">
         <f t="shared" si="4"/>
@@ -4427,18 +4439,18 @@
       </c>
       <c r="P17" s="184">
         <f t="shared" si="7"/>
-        <v>178262.45</v>
+        <v>178202.45</v>
       </c>
       <c r="Q17" s="185">
         <f t="shared" si="8"/>
-        <v>183610.45</v>
+        <v>183548.45</v>
       </c>
       <c r="R17" s="44">
         <f t="shared" si="9"/>
         <v>0.45</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="59">
         <v>2</v>
       </c>
@@ -4478,7 +4490,7 @@
       </c>
       <c r="L18" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M18" s="183">
         <f t="shared" si="4"/>
@@ -4494,11 +4506,11 @@
       </c>
       <c r="P18" s="184">
         <f t="shared" si="7"/>
-        <v>122666.46</v>
+        <v>122624.46</v>
       </c>
       <c r="Q18" s="185">
         <f t="shared" si="8"/>
-        <v>126346.46</v>
+        <v>126303.46</v>
       </c>
       <c r="R18" s="44">
         <f t="shared" si="9"/>
@@ -4506,7 +4518,7 @@
       </c>
       <c r="S18" s="114"/>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="59">
         <v>3</v>
       </c>
@@ -4546,7 +4558,7 @@
       </c>
       <c r="L19" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M19" s="183">
         <f t="shared" si="4"/>
@@ -4562,11 +4574,11 @@
       </c>
       <c r="P19" s="184">
         <f t="shared" si="7"/>
-        <v>122666.47</v>
+        <v>122624.47</v>
       </c>
       <c r="Q19" s="185">
         <f t="shared" si="8"/>
-        <v>126346.47</v>
+        <v>126303.47</v>
       </c>
       <c r="R19" s="44">
         <f t="shared" si="9"/>
@@ -4574,7 +4586,7 @@
       </c>
       <c r="S19" s="114"/>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="59">
         <v>3</v>
       </c>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="L20" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M20" s="183">
         <f t="shared" si="4"/>
@@ -4630,11 +4642,11 @@
       </c>
       <c r="P20" s="184">
         <f t="shared" si="7"/>
-        <v>178262.48</v>
+        <v>178202.48</v>
       </c>
       <c r="Q20" s="185">
         <f t="shared" si="8"/>
-        <v>183610.48</v>
+        <v>183548.48</v>
       </c>
       <c r="R20" s="44">
         <f t="shared" si="9"/>
@@ -4643,7 +4655,7 @@
       <c r="S20" s="114"/>
       <c r="T20" s="43"/>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="59">
         <v>4</v>
       </c>
@@ -4682,7 +4694,7 @@
       </c>
       <c r="L21" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M21" s="183">
         <f t="shared" si="4"/>
@@ -4698,18 +4710,18 @@
       </c>
       <c r="P21" s="184">
         <f t="shared" si="7"/>
-        <v>173127.49</v>
+        <v>173067.49</v>
       </c>
       <c r="Q21" s="185">
         <f t="shared" si="8"/>
-        <v>178321.49</v>
+        <v>178259.49</v>
       </c>
       <c r="R21" s="44">
         <f t="shared" si="9"/>
         <v>0.49</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="59">
         <v>4</v>
       </c>
@@ -4746,7 +4758,7 @@
       </c>
       <c r="L22" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M22" s="183">
         <f t="shared" si="4"/>
@@ -4762,18 +4774,18 @@
       </c>
       <c r="P22" s="184">
         <f t="shared" si="7"/>
-        <v>491959.5</v>
+        <v>491917.5</v>
       </c>
       <c r="Q22" s="185">
         <f t="shared" si="8"/>
-        <v>506718.5</v>
+        <v>506675.5</v>
       </c>
       <c r="R22" s="44">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="59">
         <v>5</v>
       </c>
@@ -4810,7 +4822,7 @@
       </c>
       <c r="L23" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M23" s="183">
         <f t="shared" si="4"/>
@@ -4826,18 +4838,18 @@
       </c>
       <c r="P23" s="184">
         <f t="shared" si="7"/>
-        <v>397888.51</v>
+        <v>397847.51</v>
       </c>
       <c r="Q23" s="185">
         <f t="shared" si="8"/>
-        <v>409825.51</v>
+        <v>409782.51</v>
       </c>
       <c r="R23" s="44">
         <f t="shared" si="9"/>
         <v>0.51</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="59">
         <v>5</v>
       </c>
@@ -4877,7 +4889,7 @@
       </c>
       <c r="L24" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M24" s="183">
         <f t="shared" si="4"/>
@@ -4893,18 +4905,18 @@
       </c>
       <c r="P24" s="184">
         <f t="shared" si="7"/>
-        <v>178262.52</v>
+        <v>178202.52</v>
       </c>
       <c r="Q24" s="185">
         <f t="shared" si="8"/>
-        <v>183610.52</v>
+        <v>183548.52</v>
       </c>
       <c r="R24" s="44">
         <f t="shared" si="9"/>
         <v>0.52</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="59">
         <v>6</v>
       </c>
@@ -4941,7 +4953,7 @@
       </c>
       <c r="L25" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M25" s="183">
         <f t="shared" si="4"/>
@@ -4957,18 +4969,18 @@
       </c>
       <c r="P25" s="184">
         <f t="shared" si="7"/>
-        <v>215620.53</v>
+        <v>215560.53</v>
       </c>
       <c r="Q25" s="185">
         <f t="shared" si="8"/>
-        <v>222089.53</v>
+        <v>222027.53</v>
       </c>
       <c r="R25" s="44">
         <f t="shared" si="9"/>
         <v>0.53</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="59">
         <v>6</v>
       </c>
@@ -5008,7 +5020,7 @@
       </c>
       <c r="L26" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M26" s="183">
         <f t="shared" si="4"/>
@@ -5024,18 +5036,18 @@
       </c>
       <c r="P26" s="184">
         <f t="shared" si="7"/>
-        <v>122666.54</v>
+        <v>122624.54</v>
       </c>
       <c r="Q26" s="185">
         <f t="shared" si="8"/>
-        <v>126346.54</v>
+        <v>126303.54</v>
       </c>
       <c r="R26" s="44">
         <f t="shared" si="9"/>
         <v>0.54</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="59">
         <v>7</v>
       </c>
@@ -5074,7 +5086,7 @@
       </c>
       <c r="L27" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M27" s="183">
         <f t="shared" si="4"/>
@@ -5090,18 +5102,18 @@
       </c>
       <c r="P27" s="184">
         <f t="shared" si="7"/>
-        <v>247315.55</v>
+        <v>247274.55</v>
       </c>
       <c r="Q27" s="185">
         <f t="shared" si="8"/>
-        <v>254734.55</v>
+        <v>254692.55</v>
       </c>
       <c r="R27" s="44">
         <f t="shared" si="9"/>
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="59">
         <v>7</v>
       </c>
@@ -5141,7 +5153,7 @@
       </c>
       <c r="L28" s="168">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M28" s="169">
         <f t="shared" si="4"/>
@@ -5157,18 +5169,18 @@
       </c>
       <c r="P28" s="170">
         <f t="shared" si="7"/>
-        <v>220441.56</v>
+        <v>220380.56</v>
       </c>
       <c r="Q28" s="171">
         <f t="shared" si="8"/>
-        <v>227054.56</v>
+        <v>226991.56</v>
       </c>
       <c r="R28" s="44">
         <f t="shared" si="9"/>
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="59">
         <v>8</v>
       </c>
@@ -5206,7 +5218,7 @@
       </c>
       <c r="L29" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M29" s="183">
         <f t="shared" si="4"/>
@@ -5222,18 +5234,18 @@
       </c>
       <c r="P29" s="184">
         <f t="shared" si="7"/>
-        <v>7095.57</v>
+        <v>7034.57</v>
       </c>
       <c r="Q29" s="185">
         <f t="shared" si="8"/>
-        <v>7308.57</v>
+        <v>7245.57</v>
       </c>
       <c r="R29" s="44">
         <f t="shared" si="9"/>
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="59">
         <v>8</v>
       </c>
@@ -5272,7 +5284,7 @@
       </c>
       <c r="L30" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M30" s="183">
         <f t="shared" si="4"/>
@@ -5288,18 +5300,18 @@
       </c>
       <c r="P30" s="184">
         <f t="shared" si="7"/>
-        <v>115800.58</v>
+        <v>115758.58</v>
       </c>
       <c r="Q30" s="185">
         <f t="shared" si="8"/>
-        <v>119274.58</v>
+        <v>119231.58</v>
       </c>
       <c r="R30" s="44">
         <f t="shared" si="9"/>
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="59">
         <v>9</v>
       </c>
@@ -5334,7 +5346,7 @@
       </c>
       <c r="L31" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M31" s="183">
         <f t="shared" si="4"/>
@@ -5350,18 +5362,18 @@
       </c>
       <c r="P31" s="184">
         <f t="shared" si="7"/>
-        <v>243983.59</v>
+        <v>243941.59</v>
       </c>
       <c r="Q31" s="185">
         <f t="shared" si="8"/>
-        <v>251303.59</v>
+        <v>251259.59</v>
       </c>
       <c r="R31" s="44">
         <f t="shared" si="9"/>
         <v>0.59</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="59">
         <v>9</v>
       </c>
@@ -5399,7 +5411,7 @@
       </c>
       <c r="L32" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M32" s="183">
         <f t="shared" si="4"/>
@@ -5415,18 +5427,18 @@
       </c>
       <c r="P32" s="184">
         <f t="shared" si="7"/>
-        <v>178262.6</v>
+        <v>178202.6</v>
       </c>
       <c r="Q32" s="185">
         <f t="shared" si="8"/>
-        <v>183610.6</v>
+        <v>183548.6</v>
       </c>
       <c r="R32" s="44">
         <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="59">
         <v>10</v>
       </c>
@@ -5464,7 +5476,7 @@
       </c>
       <c r="L33" s="168">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M33" s="169">
         <f t="shared" si="4"/>
@@ -5480,18 +5492,18 @@
       </c>
       <c r="P33" s="170">
         <f t="shared" si="7"/>
-        <v>177716.61</v>
+        <v>177655.61</v>
       </c>
       <c r="Q33" s="171">
         <f t="shared" si="8"/>
-        <v>183047.61</v>
+        <v>182985.61</v>
       </c>
       <c r="R33" s="44">
         <f t="shared" si="9"/>
         <v>0.61</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="59">
         <v>10</v>
       </c>
@@ -5528,7 +5540,7 @@
       </c>
       <c r="L34" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M34" s="183">
         <f t="shared" si="4"/>
@@ -5544,18 +5556,18 @@
       </c>
       <c r="P34" s="184">
         <f t="shared" si="7"/>
-        <v>243983.62</v>
+        <v>243941.62</v>
       </c>
       <c r="Q34" s="185">
         <f t="shared" si="8"/>
-        <v>251303.62</v>
+        <v>251259.62</v>
       </c>
       <c r="R34" s="44">
         <f t="shared" si="9"/>
         <v>0.62</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="59">
         <v>11</v>
       </c>
@@ -5595,7 +5607,7 @@
       </c>
       <c r="L35" s="182">
         <f t="shared" si="3"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M35" s="183">
         <f t="shared" si="4"/>
@@ -5611,18 +5623,18 @@
       </c>
       <c r="P35" s="184">
         <f t="shared" si="7"/>
-        <v>122666.63</v>
+        <v>122624.63</v>
       </c>
       <c r="Q35" s="185">
         <f t="shared" si="8"/>
-        <v>126346.63</v>
+        <v>126303.63</v>
       </c>
       <c r="R35" s="44">
         <f t="shared" si="9"/>
         <v>0.63</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="59">
         <v>11</v>
       </c>
@@ -5662,7 +5674,7 @@
       </c>
       <c r="L36" s="182">
         <f t="shared" si="3"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M36" s="183">
         <f t="shared" si="4"/>
@@ -5678,18 +5690,18 @@
       </c>
       <c r="P36" s="184">
         <f t="shared" si="7"/>
-        <v>178262.64</v>
+        <v>178202.64</v>
       </c>
       <c r="Q36" s="185">
         <f t="shared" si="8"/>
-        <v>183610.64</v>
+        <v>183548.64</v>
       </c>
       <c r="R36" s="44">
         <f t="shared" si="9"/>
         <v>0.64</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="59">
         <v>12</v>
       </c>
@@ -5729,7 +5741,7 @@
       </c>
       <c r="L37" s="182">
         <f t="shared" ref="L37:L68" si="14">M$1*F37</f>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M37" s="183">
         <f t="shared" ref="M37:M56" si="15">F$1*F37</f>
@@ -5745,18 +5757,18 @@
       </c>
       <c r="P37" s="184">
         <f t="shared" ref="P37:P68" si="18">ROUND(SUM(I37:O37),0) + R37</f>
-        <v>178262.65</v>
+        <v>178202.65</v>
       </c>
       <c r="Q37" s="185">
         <f t="shared" ref="Q37:Q56" si="19">ROUND(P37*3%,0) + P37</f>
-        <v>183610.65</v>
+        <v>183548.65</v>
       </c>
       <c r="R37" s="44">
         <f t="shared" ref="R37:R68" si="20">ROUND(0.001+C37/100,2)</f>
         <v>0.65</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="59">
         <v>12</v>
       </c>
@@ -5793,7 +5805,7 @@
       </c>
       <c r="L38" s="182">
         <f t="shared" si="14"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M38" s="183">
         <f t="shared" si="15"/>
@@ -5809,18 +5821,18 @@
       </c>
       <c r="P38" s="184">
         <f t="shared" si="18"/>
-        <v>476973.66</v>
+        <v>476931.66</v>
       </c>
       <c r="Q38" s="185">
         <f t="shared" si="19"/>
-        <v>491282.66</v>
+        <v>491239.66</v>
       </c>
       <c r="R38" s="44">
         <f t="shared" si="20"/>
         <v>0.66</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="59">
         <v>1</v>
       </c>
@@ -5860,7 +5872,7 @@
       </c>
       <c r="L39" s="182">
         <f t="shared" si="14"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M39" s="183">
         <f t="shared" si="15"/>
@@ -5876,18 +5888,18 @@
       </c>
       <c r="P39" s="184">
         <f t="shared" si="18"/>
-        <v>122666.67</v>
+        <v>122624.67</v>
       </c>
       <c r="Q39" s="185">
         <f t="shared" si="19"/>
-        <v>126346.67</v>
+        <v>126303.67</v>
       </c>
       <c r="R39" s="44">
         <f t="shared" si="20"/>
         <v>0.67</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="59">
         <v>1</v>
       </c>
@@ -5927,7 +5939,7 @@
       </c>
       <c r="L40" s="182">
         <f t="shared" si="14"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M40" s="183">
         <f t="shared" si="15"/>
@@ -5943,18 +5955,18 @@
       </c>
       <c r="P40" s="184">
         <f t="shared" si="18"/>
-        <v>298254.68</v>
+        <v>298194.68</v>
       </c>
       <c r="Q40" s="185">
         <f t="shared" si="19"/>
-        <v>307202.68</v>
+        <v>307140.68</v>
       </c>
       <c r="R40" s="44">
         <f t="shared" si="20"/>
         <v>0.68</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="59">
         <v>1</v>
       </c>
@@ -5994,7 +6006,7 @@
       </c>
       <c r="L41" s="168">
         <f t="shared" si="14"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M41" s="169">
         <f t="shared" si="15"/>
@@ -6010,18 +6022,18 @@
       </c>
       <c r="P41" s="170">
         <f t="shared" si="18"/>
-        <v>178262.69</v>
+        <v>178202.69</v>
       </c>
       <c r="Q41" s="171">
         <f t="shared" si="19"/>
-        <v>183610.69</v>
+        <v>183548.69</v>
       </c>
       <c r="R41" s="44">
         <f t="shared" si="20"/>
         <v>0.69</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="59">
         <v>2</v>
       </c>
@@ -6061,7 +6073,7 @@
       </c>
       <c r="L42" s="182">
         <f t="shared" si="14"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M42" s="183">
         <f t="shared" si="15"/>
@@ -6077,18 +6089,18 @@
       </c>
       <c r="P42" s="184">
         <f t="shared" si="18"/>
-        <v>239438.7</v>
+        <v>239396.7</v>
       </c>
       <c r="Q42" s="185">
         <f t="shared" si="19"/>
-        <v>246621.7</v>
+        <v>246578.7</v>
       </c>
       <c r="R42" s="44">
         <f t="shared" si="20"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="59">
         <v>2</v>
       </c>
@@ -6128,7 +6140,7 @@
       </c>
       <c r="L43" s="182">
         <f t="shared" si="14"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M43" s="183">
         <f t="shared" si="15"/>
@@ -6144,18 +6156,18 @@
       </c>
       <c r="P43" s="184">
         <f t="shared" si="18"/>
-        <v>122666.71</v>
+        <v>122624.71</v>
       </c>
       <c r="Q43" s="185">
         <f t="shared" si="19"/>
-        <v>126346.71</v>
+        <v>126303.71</v>
       </c>
       <c r="R43" s="44">
         <f t="shared" si="20"/>
         <v>0.71</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="59">
         <v>2</v>
       </c>
@@ -6194,7 +6206,7 @@
       </c>
       <c r="L44" s="182">
         <f t="shared" si="14"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M44" s="183">
         <f t="shared" si="15"/>
@@ -6210,18 +6222,18 @@
       </c>
       <c r="P44" s="184">
         <f t="shared" si="18"/>
-        <v>694431.72</v>
+        <v>694371.72</v>
       </c>
       <c r="Q44" s="185">
         <f t="shared" si="19"/>
-        <v>715264.72</v>
+        <v>715202.72</v>
       </c>
       <c r="R44" s="44">
         <f t="shared" si="20"/>
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="59">
         <v>3</v>
       </c>
@@ -6258,7 +6270,7 @@
       </c>
       <c r="L45" s="182">
         <f t="shared" si="14"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M45" s="183">
         <f t="shared" si="15"/>
@@ -6274,18 +6286,18 @@
       </c>
       <c r="P45" s="184">
         <f t="shared" si="18"/>
-        <v>873531.73</v>
+        <v>873470.73</v>
       </c>
       <c r="Q45" s="185">
         <f t="shared" si="19"/>
-        <v>899737.73</v>
+        <v>899674.73</v>
       </c>
       <c r="R45" s="44">
         <f t="shared" si="20"/>
         <v>0.73</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="59">
         <v>3</v>
       </c>
@@ -6325,7 +6337,7 @@
       </c>
       <c r="L46" s="182">
         <f t="shared" si="14"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M46" s="183">
         <f t="shared" si="15"/>
@@ -6341,18 +6353,18 @@
       </c>
       <c r="P46" s="184">
         <f t="shared" si="18"/>
-        <v>122666.74</v>
+        <v>122624.74</v>
       </c>
       <c r="Q46" s="185">
         <f t="shared" si="19"/>
-        <v>126346.74</v>
+        <v>126303.74</v>
       </c>
       <c r="R46" s="44">
         <f t="shared" si="20"/>
         <v>0.74</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="60">
         <v>3</v>
       </c>
@@ -6389,7 +6401,7 @@
       </c>
       <c r="L47" s="69">
         <f t="shared" si="14"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M47" s="120">
         <f t="shared" si="15"/>
@@ -6405,11 +6417,11 @@
       </c>
       <c r="P47" s="70">
         <f t="shared" si="18"/>
-        <v>358383.75</v>
+        <v>358341.75</v>
       </c>
       <c r="Q47" s="71">
         <f t="shared" si="19"/>
-        <v>369135.75</v>
+        <v>369091.75</v>
       </c>
       <c r="R47" s="44">
         <f t="shared" si="20"/>
@@ -6417,7 +6429,7 @@
       </c>
       <c r="T47" s="114"/>
     </row>
-    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="60">
         <v>4</v>
       </c>
@@ -6457,7 +6469,7 @@
       </c>
       <c r="L48" s="69">
         <f t="shared" si="14"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M48" s="120">
         <f t="shared" si="15"/>
@@ -6473,18 +6485,18 @@
       </c>
       <c r="P48" s="70">
         <f t="shared" si="18"/>
-        <v>178262.76</v>
+        <v>178202.76</v>
       </c>
       <c r="Q48" s="71">
         <f t="shared" si="19"/>
-        <v>183610.76</v>
+        <v>183548.76</v>
       </c>
       <c r="R48" s="44">
         <f t="shared" si="20"/>
         <v>0.76</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="60">
         <v>4</v>
       </c>
@@ -6523,7 +6535,7 @@
       </c>
       <c r="L49" s="69">
         <f t="shared" si="14"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M49" s="120">
         <f t="shared" si="15"/>
@@ -6539,18 +6551,18 @@
       </c>
       <c r="P49" s="70">
         <f t="shared" si="18"/>
-        <v>181065.77</v>
+        <v>181004.77</v>
       </c>
       <c r="Q49" s="71">
         <f t="shared" si="19"/>
-        <v>186497.77</v>
+        <v>186434.77</v>
       </c>
       <c r="R49" s="44">
         <f t="shared" si="20"/>
         <v>0.77</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="60">
         <v>4</v>
       </c>
@@ -6590,7 +6602,7 @@
       </c>
       <c r="L50" s="69">
         <f t="shared" si="14"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M50" s="120">
         <f t="shared" si="15"/>
@@ -6606,18 +6618,18 @@
       </c>
       <c r="P50" s="70">
         <f t="shared" si="18"/>
-        <v>122666.78</v>
+        <v>122624.78</v>
       </c>
       <c r="Q50" s="71">
         <f t="shared" si="19"/>
-        <v>126346.78</v>
+        <v>126303.78</v>
       </c>
       <c r="R50" s="44">
         <f t="shared" si="20"/>
         <v>0.78</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="60">
         <v>5</v>
       </c>
@@ -6655,7 +6667,7 @@
       </c>
       <c r="L51" s="182">
         <f t="shared" si="14"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M51" s="183">
         <f t="shared" si="15"/>
@@ -6671,11 +6683,11 @@
       </c>
       <c r="P51" s="184">
         <f t="shared" si="18"/>
-        <v>122666.79</v>
+        <v>122624.79</v>
       </c>
       <c r="Q51" s="185">
         <f t="shared" si="19"/>
-        <v>126346.79</v>
+        <v>126303.79</v>
       </c>
       <c r="R51" s="200">
         <f t="shared" si="20"/>
@@ -6683,7 +6695,7 @@
       </c>
       <c r="S51" s="201"/>
     </row>
-    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="60">
         <v>5</v>
       </c>
@@ -6723,7 +6735,7 @@
       </c>
       <c r="L52" s="69">
         <f t="shared" si="14"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M52" s="120">
         <f t="shared" si="15"/>
@@ -6739,18 +6751,18 @@
       </c>
       <c r="P52" s="70">
         <f t="shared" si="18"/>
-        <v>178262.8</v>
+        <v>178202.8</v>
       </c>
       <c r="Q52" s="71">
         <f t="shared" si="19"/>
-        <v>183610.8</v>
+        <v>183548.79999999999</v>
       </c>
       <c r="R52" s="44">
         <f t="shared" si="20"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="60">
         <v>5</v>
       </c>
@@ -6790,7 +6802,7 @@
       </c>
       <c r="L53" s="69">
         <f t="shared" si="14"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M53" s="120">
         <f t="shared" si="15"/>
@@ -6806,11 +6818,11 @@
       </c>
       <c r="P53" s="70">
         <f t="shared" si="18"/>
-        <v>219874.81</v>
+        <v>219814.81</v>
       </c>
       <c r="Q53" s="71">
         <f t="shared" si="19"/>
-        <v>226470.81</v>
+        <v>226408.81</v>
       </c>
       <c r="R53" s="44">
         <f t="shared" si="20"/>
@@ -6820,7 +6832,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="60">
         <v>6</v>
       </c>
@@ -6858,7 +6870,7 @@
       </c>
       <c r="L54" s="69">
         <f t="shared" si="14"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M54" s="120">
         <f t="shared" si="15"/>
@@ -6874,18 +6886,18 @@
       </c>
       <c r="P54" s="70">
         <f t="shared" si="18"/>
-        <v>122666.82</v>
+        <v>122624.82</v>
       </c>
       <c r="Q54" s="71">
         <f t="shared" si="19"/>
-        <v>126346.82</v>
+        <v>126303.82</v>
       </c>
       <c r="R54" s="44">
         <f t="shared" si="20"/>
         <v>0.82</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="60">
         <v>6</v>
       </c>
@@ -6925,7 +6937,7 @@
       </c>
       <c r="L55" s="182">
         <f t="shared" si="14"/>
-        <v>71531.36323599999</v>
+        <v>71489.663235999993</v>
       </c>
       <c r="M55" s="183">
         <f t="shared" si="15"/>
@@ -6941,18 +6953,18 @@
       </c>
       <c r="P55" s="184">
         <f t="shared" si="18"/>
-        <v>122666.83</v>
+        <v>122624.83</v>
       </c>
       <c r="Q55" s="185">
         <f t="shared" si="19"/>
-        <v>126346.83</v>
+        <v>126303.83</v>
       </c>
       <c r="R55" s="44">
         <f t="shared" si="20"/>
         <v>0.83</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="60">
         <v>6</v>
       </c>
@@ -6989,7 +7001,7 @@
       </c>
       <c r="L56" s="182">
         <f t="shared" si="14"/>
-        <v>103952.05304799999</v>
+        <v>103891.45304799998</v>
       </c>
       <c r="M56" s="183">
         <f t="shared" si="15"/>
@@ -7005,18 +7017,18 @@
       </c>
       <c r="P56" s="184">
         <f t="shared" si="18"/>
-        <v>178262.84</v>
+        <v>178202.84</v>
       </c>
       <c r="Q56" s="185">
         <f t="shared" si="19"/>
-        <v>183610.84</v>
+        <v>183548.84</v>
       </c>
       <c r="R56" s="44">
         <f t="shared" si="20"/>
         <v>0.84</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="60">
         <v>7</v>
       </c>
@@ -7050,7 +7062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="60">
         <v>7</v>
       </c>
@@ -7084,7 +7096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="60">
         <v>7</v>
       </c>
@@ -7124,7 +7136,7 @@
       </c>
       <c r="L59" s="182">
         <f t="shared" si="14"/>
-        <v>16467.651967999998</v>
+        <v>16458.051968</v>
       </c>
       <c r="M59" s="183">
         <f t="shared" ref="M59:M90" si="24">F$1*F59</f>
@@ -7140,18 +7152,18 @@
       </c>
       <c r="P59" s="184">
         <f t="shared" si="18"/>
-        <v>28240.17</v>
+        <v>28230.17</v>
       </c>
       <c r="Q59" s="185">
         <f t="shared" ref="Q59:Q90" si="26">ROUND(P59*3%,0) + P59</f>
-        <v>29087.17</v>
+        <v>29077.17</v>
       </c>
       <c r="R59" s="44">
         <f t="shared" si="20"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="60">
         <v>8</v>
       </c>
@@ -7188,7 +7200,7 @@
       </c>
       <c r="L60" s="182">
         <f t="shared" si="14"/>
-        <v>16982.266091999998</v>
+        <v>16972.366091999997</v>
       </c>
       <c r="M60" s="183">
         <f t="shared" si="24"/>
@@ -7204,18 +7216,18 @@
       </c>
       <c r="P60" s="184">
         <f t="shared" si="18"/>
-        <v>181226.18</v>
+        <v>181217.18</v>
       </c>
       <c r="Q60" s="185">
         <f t="shared" si="26"/>
-        <v>186663.18</v>
+        <v>186654.18</v>
       </c>
       <c r="R60" s="44">
         <f t="shared" si="20"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="60">
         <v>8</v>
       </c>
@@ -7250,7 +7262,7 @@
       </c>
       <c r="L61" s="182">
         <f t="shared" si="14"/>
-        <v>2058.4564959999998</v>
+        <v>2057.256496</v>
       </c>
       <c r="M61" s="183">
         <f t="shared" si="24"/>
@@ -7266,18 +7278,18 @@
       </c>
       <c r="P61" s="184">
         <f t="shared" si="18"/>
-        <v>21133.19</v>
+        <v>21132.19</v>
       </c>
       <c r="Q61" s="185">
         <f t="shared" si="26"/>
-        <v>21767.19</v>
+        <v>21766.19</v>
       </c>
       <c r="R61" s="44">
         <f t="shared" si="20"/>
         <v>0.19</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="60">
         <v>8</v>
       </c>
@@ -7314,7 +7326,7 @@
       </c>
       <c r="L62" s="182">
         <f t="shared" si="14"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M62" s="183">
         <f t="shared" si="24"/>
@@ -7330,18 +7342,18 @@
       </c>
       <c r="P62" s="184">
         <f t="shared" si="18"/>
-        <v>1718.2</v>
+        <v>1717.2</v>
       </c>
       <c r="Q62" s="185">
         <f t="shared" si="26"/>
-        <v>1770.2</v>
+        <v>1769.2</v>
       </c>
       <c r="R62" s="44">
         <f t="shared" si="20"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="60">
         <v>9</v>
       </c>
@@ -7378,7 +7390,7 @@
       </c>
       <c r="L63" s="182">
         <f t="shared" si="14"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M63" s="183">
         <f t="shared" si="24"/>
@@ -7405,7 +7417,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="60">
         <v>9</v>
       </c>
@@ -7443,7 +7455,7 @@
       </c>
       <c r="L64" s="182">
         <f t="shared" si="14"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M64" s="183">
         <f t="shared" si="24"/>
@@ -7459,18 +7471,18 @@
       </c>
       <c r="P64" s="184">
         <f t="shared" si="18"/>
-        <v>1765.22</v>
+        <v>1764.22</v>
       </c>
       <c r="Q64" s="185">
         <f t="shared" si="26"/>
-        <v>1818.22</v>
+        <v>1817.22</v>
       </c>
       <c r="R64" s="44">
         <f t="shared" si="20"/>
         <v>0.22</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="60">
         <v>9</v>
       </c>
@@ -7510,7 +7522,7 @@
       </c>
       <c r="L65" s="182">
         <f t="shared" si="14"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M65" s="183">
         <f t="shared" si="24"/>
@@ -7526,18 +7538,18 @@
       </c>
       <c r="P65" s="184">
         <f t="shared" si="18"/>
-        <v>1765.23</v>
+        <v>1764.23</v>
       </c>
       <c r="Q65" s="185">
         <f t="shared" si="26"/>
-        <v>1818.23</v>
+        <v>1817.23</v>
       </c>
       <c r="R65" s="44">
         <f t="shared" si="20"/>
         <v>0.23</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="60">
         <v>10</v>
       </c>
@@ -7575,7 +7587,7 @@
       </c>
       <c r="L66" s="182">
         <f t="shared" si="14"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M66" s="183">
         <f t="shared" si="24"/>
@@ -7591,18 +7603,18 @@
       </c>
       <c r="P66" s="184">
         <f t="shared" si="18"/>
-        <v>1765.24</v>
+        <v>1764.24</v>
       </c>
       <c r="Q66" s="185">
         <f t="shared" si="26"/>
-        <v>1818.24</v>
+        <v>1817.24</v>
       </c>
       <c r="R66" s="44">
         <f t="shared" si="20"/>
         <v>0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="60">
         <v>10</v>
       </c>
@@ -7642,7 +7654,7 @@
       </c>
       <c r="L67" s="182">
         <f t="shared" si="14"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M67" s="183">
         <f t="shared" si="24"/>
@@ -7658,18 +7670,18 @@
       </c>
       <c r="P67" s="184">
         <f t="shared" si="18"/>
-        <v>1765.25</v>
+        <v>1764.25</v>
       </c>
       <c r="Q67" s="185">
         <f t="shared" si="26"/>
-        <v>1818.25</v>
+        <v>1817.25</v>
       </c>
       <c r="R67" s="44">
         <f t="shared" si="20"/>
         <v>0.25</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="60">
         <v>10</v>
       </c>
@@ -7709,7 +7721,7 @@
       </c>
       <c r="L68" s="182">
         <f t="shared" si="14"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M68" s="183">
         <f t="shared" si="24"/>
@@ -7725,18 +7737,18 @@
       </c>
       <c r="P68" s="184">
         <f t="shared" si="18"/>
-        <v>1765.26</v>
+        <v>1764.26</v>
       </c>
       <c r="Q68" s="185">
         <f t="shared" si="26"/>
-        <v>1818.26</v>
+        <v>1817.26</v>
       </c>
       <c r="R68" s="44">
         <f t="shared" si="20"/>
         <v>0.26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="60">
         <v>11</v>
       </c>
@@ -7771,7 +7783,7 @@
       </c>
       <c r="L69" s="182">
         <f t="shared" ref="L69:L90" si="27">M$1*F69</f>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M69" s="183">
         <f t="shared" si="24"/>
@@ -7798,7 +7810,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="60">
         <v>11</v>
       </c>
@@ -7833,7 +7845,7 @@
       </c>
       <c r="L70" s="182">
         <f t="shared" si="27"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M70" s="183">
         <f t="shared" si="24"/>
@@ -7860,7 +7872,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="60">
         <v>11</v>
       </c>
@@ -7897,7 +7909,7 @@
       </c>
       <c r="L71" s="182">
         <f t="shared" si="27"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M71" s="183">
         <f t="shared" si="24"/>
@@ -7913,18 +7925,18 @@
       </c>
       <c r="P71" s="184">
         <f t="shared" si="29"/>
-        <v>5158.29</v>
+        <v>5157.29</v>
       </c>
       <c r="Q71" s="185">
         <f t="shared" si="26"/>
-        <v>5313.29</v>
+        <v>5312.29</v>
       </c>
       <c r="R71" s="44">
         <f t="shared" si="30"/>
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="60"/>
       <c r="B72" s="175" t="s">
         <v>221</v>
@@ -7959,7 +7971,7 @@
       </c>
       <c r="L72" s="182">
         <f t="shared" si="27"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M72" s="183">
         <f t="shared" si="24"/>
@@ -7986,7 +7998,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="60"/>
       <c r="B73" s="175" t="s">
         <v>222</v>
@@ -8019,7 +8031,7 @@
       </c>
       <c r="L73" s="182">
         <f t="shared" si="27"/>
-        <v>1029.2282479999999</v>
+        <v>1028.628248</v>
       </c>
       <c r="M73" s="183">
         <f t="shared" si="24"/>
@@ -8046,7 +8058,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="60"/>
       <c r="B74" s="175" t="s">
         <v>223</v>
@@ -8079,7 +8091,7 @@
       </c>
       <c r="L74" s="182">
         <f t="shared" si="27"/>
-        <v>81309.031591999999</v>
+        <v>81261.631591999991</v>
       </c>
       <c r="M74" s="183">
         <f t="shared" si="24"/>
@@ -8094,18 +8106,18 @@
       </c>
       <c r="P74" s="184">
         <f t="shared" si="29"/>
-        <v>3724059.32</v>
+        <v>3724012.32</v>
       </c>
       <c r="Q74" s="185">
         <f t="shared" si="26"/>
-        <v>3835781.32</v>
+        <v>3835732.32</v>
       </c>
       <c r="R74" s="44">
         <f t="shared" si="30"/>
         <v>0.32</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="60"/>
       <c r="B75" s="175" t="s">
         <v>225</v>
@@ -8138,7 +8150,7 @@
       </c>
       <c r="L75" s="182">
         <f t="shared" si="27"/>
-        <v>31391.461563999997</v>
+        <v>31373.161563999998</v>
       </c>
       <c r="M75" s="183">
         <f t="shared" si="24"/>
@@ -8154,18 +8166,18 @@
       </c>
       <c r="P75" s="184">
         <f t="shared" si="29"/>
-        <v>583527.01</v>
+        <v>583508.01</v>
       </c>
       <c r="Q75" s="185">
         <f t="shared" si="26"/>
-        <v>601033.01</v>
+        <v>601013.01</v>
       </c>
       <c r="R75" s="44">
         <f t="shared" si="30"/>
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="60"/>
       <c r="B76" s="175" t="s">
         <v>226</v>
@@ -8198,7 +8210,7 @@
       </c>
       <c r="L76" s="182">
         <f t="shared" si="27"/>
-        <v>32935.303935999997</v>
+        <v>32916.103936</v>
       </c>
       <c r="M76" s="183">
         <f t="shared" si="24"/>
@@ -8214,18 +8226,18 @@
       </c>
       <c r="P76" s="184">
         <f t="shared" si="29"/>
-        <v>165010.01999999999</v>
+        <v>164991.01999999999</v>
       </c>
       <c r="Q76" s="185">
         <f t="shared" si="26"/>
-        <v>169960.02</v>
+        <v>169941.02</v>
       </c>
       <c r="R76" s="44">
         <f t="shared" si="30"/>
         <v>0.02</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="60"/>
       <c r="B77" s="175" t="s">
         <v>228</v>
@@ -8261,7 +8273,7 @@
       </c>
       <c r="L77" s="182">
         <f t="shared" si="27"/>
-        <v>29333.005067999999</v>
+        <v>29315.905067999996</v>
       </c>
       <c r="M77" s="183">
         <f t="shared" si="24"/>
@@ -8277,18 +8289,18 @@
       </c>
       <c r="P77" s="184">
         <f t="shared" si="29"/>
-        <v>50302.03</v>
+        <v>50285.03</v>
       </c>
       <c r="Q77" s="185">
         <f t="shared" si="26"/>
-        <v>51811.03</v>
+        <v>51794.03</v>
       </c>
       <c r="R77" s="44">
         <f t="shared" si="30"/>
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="60"/>
       <c r="B78" s="175" t="s">
         <v>230</v>
@@ -8323,7 +8335,7 @@
       </c>
       <c r="L78" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M78" s="183">
         <f t="shared" si="24"/>
@@ -8339,18 +8351,18 @@
       </c>
       <c r="P78" s="184">
         <f t="shared" si="29"/>
-        <v>45425.04</v>
+        <v>45409.04</v>
       </c>
       <c r="Q78" s="185">
         <f t="shared" si="26"/>
-        <v>46788.04</v>
+        <v>46771.040000000001</v>
       </c>
       <c r="R78" s="44">
         <f t="shared" si="30"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="60"/>
       <c r="B79" s="175" t="s">
         <v>231</v>
@@ -8388,7 +8400,7 @@
       </c>
       <c r="L79" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M79" s="183">
         <f t="shared" si="24"/>
@@ -8404,18 +8416,18 @@
       </c>
       <c r="P79" s="184">
         <f t="shared" si="29"/>
-        <v>36172.050000000003</v>
+        <v>36156.050000000003</v>
       </c>
       <c r="Q79" s="185">
         <f t="shared" si="26"/>
-        <v>37257.050000000003</v>
+        <v>37241.050000000003</v>
       </c>
       <c r="R79" s="44">
         <f t="shared" si="30"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="60"/>
       <c r="B80" s="175" t="s">
         <v>232</v>
@@ -8453,7 +8465,7 @@
       </c>
       <c r="L80" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M80" s="183">
         <f t="shared" si="24"/>
@@ -8469,11 +8481,11 @@
       </c>
       <c r="P80" s="184">
         <f t="shared" si="29"/>
-        <v>46772.06</v>
+        <v>46756.06</v>
       </c>
       <c r="Q80" s="185">
         <f t="shared" si="26"/>
-        <v>48175.06</v>
+        <v>48159.06</v>
       </c>
       <c r="R80" s="44">
         <f t="shared" si="30"/>
@@ -8481,7 +8493,7 @@
       </c>
       <c r="S80" s="114"/>
     </row>
-    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="60">
         <v>12</v>
       </c>
@@ -8518,7 +8530,7 @@
       </c>
       <c r="L81" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M81" s="183">
         <f t="shared" si="24"/>
@@ -8534,18 +8546,18 @@
       </c>
       <c r="P81" s="184">
         <f t="shared" si="29"/>
-        <v>93029.07</v>
+        <v>93013.07</v>
       </c>
       <c r="Q81" s="185">
         <f t="shared" si="26"/>
-        <v>95820.07</v>
+        <v>95803.07</v>
       </c>
       <c r="R81" s="44">
         <f t="shared" si="30"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="60">
         <v>12</v>
       </c>
@@ -8580,7 +8592,7 @@
       </c>
       <c r="L82" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M82" s="183">
         <f t="shared" si="24"/>
@@ -8596,18 +8608,18 @@
       </c>
       <c r="P82" s="184">
         <f t="shared" si="29"/>
-        <v>391472.08</v>
+        <v>391456.08</v>
       </c>
       <c r="Q82" s="185">
         <f t="shared" si="26"/>
-        <v>403216.08</v>
+        <v>403200.08</v>
       </c>
       <c r="R82" s="44">
         <f t="shared" si="30"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="60">
         <v>12</v>
       </c>
@@ -8645,7 +8657,7 @@
       </c>
       <c r="L83" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M83" s="183">
         <f t="shared" si="24"/>
@@ -8661,18 +8673,18 @@
       </c>
       <c r="P83" s="184">
         <f t="shared" si="29"/>
-        <v>147288.09</v>
+        <v>147272.09</v>
       </c>
       <c r="Q83" s="185">
         <f t="shared" si="26"/>
-        <v>151707.09</v>
+        <v>151690.09</v>
       </c>
       <c r="R83" s="44">
         <f t="shared" si="30"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="60"/>
       <c r="B84" s="173" t="s">
         <v>237</v>
@@ -8705,7 +8717,7 @@
       </c>
       <c r="L84" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M84" s="183">
         <f t="shared" si="24"/>
@@ -8721,18 +8733,18 @@
       </c>
       <c r="P84" s="184">
         <f t="shared" si="29"/>
-        <v>503107.1</v>
+        <v>503091.1</v>
       </c>
       <c r="Q84" s="185">
         <f t="shared" si="26"/>
-        <v>518200.1</v>
+        <v>518184.1</v>
       </c>
       <c r="R84" s="44">
         <f t="shared" si="30"/>
         <v>0.1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="60"/>
       <c r="B85" s="173" t="s">
         <v>238</v>
@@ -8767,7 +8779,7 @@
       </c>
       <c r="L85" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M85" s="183">
         <f t="shared" si="24"/>
@@ -8783,18 +8795,18 @@
       </c>
       <c r="P85" s="184">
         <f t="shared" si="29"/>
-        <v>274345.11</v>
+        <v>274329.11</v>
       </c>
       <c r="Q85" s="185">
         <f t="shared" si="26"/>
-        <v>282575.11</v>
+        <v>282559.11</v>
       </c>
       <c r="R85" s="44">
         <f t="shared" si="30"/>
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="60"/>
       <c r="B86" s="173" t="s">
         <v>239</v>
@@ -8832,7 +8844,7 @@
       </c>
       <c r="L86" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M86" s="183">
         <f t="shared" si="24"/>
@@ -8848,18 +8860,18 @@
       </c>
       <c r="P86" s="184">
         <f t="shared" si="29"/>
-        <v>46772.12</v>
+        <v>46756.12</v>
       </c>
       <c r="Q86" s="185">
         <f t="shared" si="26"/>
-        <v>48175.12</v>
+        <v>48159.12</v>
       </c>
       <c r="R86" s="44">
         <f t="shared" si="30"/>
         <v>0.12</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="60"/>
       <c r="B87" s="59" t="s">
         <v>240</v>
@@ -8895,7 +8907,7 @@
       </c>
       <c r="L87" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M87" s="183">
         <f t="shared" si="24"/>
@@ -8911,18 +8923,18 @@
       </c>
       <c r="P87" s="184">
         <f t="shared" si="29"/>
-        <v>46772.13</v>
+        <v>46756.13</v>
       </c>
       <c r="Q87" s="185">
         <f t="shared" si="26"/>
-        <v>48175.13</v>
+        <v>48159.13</v>
       </c>
       <c r="R87" s="44">
         <f t="shared" si="30"/>
         <v>0.13</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="60"/>
       <c r="B88" s="59" t="s">
         <v>241</v>
@@ -8959,7 +8971,7 @@
       </c>
       <c r="L88" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M88" s="183">
         <f t="shared" si="24"/>
@@ -8975,18 +8987,18 @@
       </c>
       <c r="P88" s="184">
         <f t="shared" si="29"/>
-        <v>44154.14</v>
+        <v>44138.14</v>
       </c>
       <c r="Q88" s="185">
         <f t="shared" si="26"/>
-        <v>45479.14</v>
+        <v>45462.14</v>
       </c>
       <c r="R88" s="44">
         <f t="shared" si="30"/>
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="60"/>
       <c r="B89" s="59" t="s">
         <v>243</v>
@@ -9025,7 +9037,7 @@
       </c>
       <c r="L89" s="182">
         <f t="shared" si="27"/>
-        <v>27274.548571999996</v>
+        <v>27258.648571999995</v>
       </c>
       <c r="M89" s="183">
         <f t="shared" si="24"/>
@@ -9041,18 +9053,18 @@
       </c>
       <c r="P89" s="184">
         <f t="shared" si="29"/>
-        <v>46772.15</v>
+        <v>46756.15</v>
       </c>
       <c r="Q89" s="185">
         <f t="shared" si="26"/>
-        <v>48175.15</v>
+        <v>48159.15</v>
       </c>
       <c r="R89" s="44">
         <f t="shared" si="30"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="59"/>
       <c r="B90" s="59" t="s">
         <v>244</v>
@@ -9088,7 +9100,7 @@
       </c>
       <c r="L90" s="182">
         <f t="shared" si="27"/>
-        <v>31906.075687999994</v>
+        <v>31887.475687999995</v>
       </c>
       <c r="M90" s="183">
         <f t="shared" si="24"/>
@@ -9104,18 +9116,18 @@
       </c>
       <c r="P90" s="184">
         <f t="shared" si="29"/>
-        <v>54714.16</v>
+        <v>54696.160000000003</v>
       </c>
       <c r="Q90" s="185">
         <f t="shared" si="26"/>
-        <v>56355.16</v>
+        <v>56337.16</v>
       </c>
       <c r="R90" s="44">
         <f t="shared" si="30"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="60"/>
       <c r="B91" s="129"/>
       <c r="C91" s="129"/>
@@ -9135,7 +9147,7 @@
       <c r="Q91" s="143"/>
       <c r="R91" s="44"/>
     </row>
-    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="77"/>
       <c r="B92" s="144"/>
       <c r="C92" s="145"/>
@@ -9167,7 +9179,7 @@
       </c>
       <c r="L92" s="152">
         <f t="shared" si="31"/>
-        <v>5146141.240000003</v>
+        <v>5143141.2399999937</v>
       </c>
       <c r="M92" s="152">
         <f>SUM(M5:M90)</f>
@@ -9183,161 +9195,161 @@
       </c>
       <c r="P92" s="153">
         <f>SUM(P5:P91)</f>
-        <v>17806837.699999999</v>
+        <v>17803842.699999999</v>
       </c>
       <c r="Q92" s="153">
         <f>SUM(Q5:Q91)</f>
-        <v>18341045.699999999</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+        <v>18337963.699999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D93" s="50"/>
       <c r="E93" s="50"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D94" s="248" t="s">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D94" s="230" t="s">
         <v>251</v>
       </c>
-      <c r="E94" s="248"/>
-      <c r="F94" s="248"/>
-      <c r="G94" s="248"/>
-      <c r="H94" s="248"/>
-      <c r="I94" s="248"/>
-      <c r="J94" s="248"/>
-      <c r="K94" s="248"/>
-      <c r="L94" s="248"/>
-      <c r="M94" s="248"/>
-      <c r="N94" s="248"/>
-      <c r="O94" s="248"/>
-      <c r="P94" s="248"/>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D95" s="248"/>
-      <c r="E95" s="248"/>
-      <c r="F95" s="248"/>
-      <c r="G95" s="248"/>
-      <c r="H95" s="248"/>
-      <c r="I95" s="248"/>
-      <c r="J95" s="248"/>
-      <c r="K95" s="248"/>
-      <c r="L95" s="248"/>
-      <c r="M95" s="248"/>
-      <c r="N95" s="248"/>
-      <c r="O95" s="248"/>
-      <c r="P95" s="248"/>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E94" s="230"/>
+      <c r="F94" s="230"/>
+      <c r="G94" s="230"/>
+      <c r="H94" s="230"/>
+      <c r="I94" s="230"/>
+      <c r="J94" s="230"/>
+      <c r="K94" s="230"/>
+      <c r="L94" s="230"/>
+      <c r="M94" s="230"/>
+      <c r="N94" s="230"/>
+      <c r="O94" s="230"/>
+      <c r="P94" s="230"/>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D95" s="230"/>
+      <c r="E95" s="230"/>
+      <c r="F95" s="230"/>
+      <c r="G95" s="230"/>
+      <c r="H95" s="230"/>
+      <c r="I95" s="230"/>
+      <c r="J95" s="230"/>
+      <c r="K95" s="230"/>
+      <c r="L95" s="230"/>
+      <c r="M95" s="230"/>
+      <c r="N95" s="230"/>
+      <c r="O95" s="230"/>
+      <c r="P95" s="230"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="H96" s="114"/>
     </row>
-    <row r="97" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:16" x14ac:dyDescent="0.3">
       <c r="H97" s="114"/>
     </row>
-    <row r="98" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:16" x14ac:dyDescent="0.3">
       <c r="H98" s="114"/>
     </row>
-    <row r="99" spans="4:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="212" t="str">
+    <row r="99" spans="4:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D99" s="204" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</v>
       </c>
-      <c r="E99" s="207"/>
-      <c r="F99" s="207"/>
-      <c r="G99" s="207"/>
-      <c r="H99" s="207"/>
-      <c r="I99" s="207"/>
-      <c r="J99" s="207"/>
-      <c r="K99" s="207"/>
-      <c r="L99" s="207"/>
-      <c r="M99" s="207"/>
-      <c r="N99" s="207"/>
-      <c r="O99" s="207"/>
-      <c r="P99" s="207"/>
-    </row>
-    <row r="100" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D100" s="207"/>
-      <c r="E100" s="207"/>
-      <c r="F100" s="207"/>
-      <c r="G100" s="207"/>
-      <c r="H100" s="207"/>
-      <c r="I100" s="207"/>
-      <c r="J100" s="207"/>
-      <c r="K100" s="207"/>
-      <c r="L100" s="207"/>
-      <c r="M100" s="207"/>
-      <c r="N100" s="207"/>
-      <c r="O100" s="207"/>
-      <c r="P100" s="207"/>
-    </row>
-    <row r="101" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D101" s="207"/>
-      <c r="E101" s="207"/>
-      <c r="F101" s="207"/>
-      <c r="G101" s="207"/>
-      <c r="H101" s="207"/>
-      <c r="I101" s="207"/>
-      <c r="J101" s="207"/>
-      <c r="K101" s="207"/>
-      <c r="L101" s="207"/>
-      <c r="M101" s="207"/>
-      <c r="N101" s="207"/>
-      <c r="O101" s="207"/>
-      <c r="P101" s="207"/>
-    </row>
-    <row r="102" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="207"/>
-      <c r="E102" s="207"/>
-      <c r="F102" s="207"/>
-      <c r="G102" s="207"/>
-      <c r="H102" s="207"/>
-      <c r="I102" s="207"/>
-      <c r="J102" s="207"/>
-      <c r="K102" s="207"/>
-      <c r="L102" s="207"/>
-      <c r="M102" s="207"/>
-      <c r="N102" s="207"/>
-      <c r="O102" s="207"/>
-      <c r="P102" s="207"/>
-    </row>
-    <row r="103" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D103" s="207"/>
-      <c r="E103" s="207"/>
-      <c r="F103" s="207"/>
-      <c r="G103" s="207"/>
-      <c r="H103" s="207"/>
-      <c r="I103" s="207"/>
-      <c r="J103" s="207"/>
-      <c r="K103" s="207"/>
-      <c r="L103" s="207"/>
-      <c r="M103" s="207"/>
-      <c r="N103" s="207"/>
-      <c r="O103" s="207"/>
-      <c r="P103" s="207"/>
-    </row>
-    <row r="104" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D104" s="207"/>
-      <c r="E104" s="207"/>
-      <c r="F104" s="207"/>
-      <c r="G104" s="207"/>
-      <c r="H104" s="207"/>
-      <c r="I104" s="207"/>
-      <c r="J104" s="207"/>
-      <c r="K104" s="207"/>
-      <c r="L104" s="207"/>
-      <c r="M104" s="207"/>
-      <c r="N104" s="207"/>
-      <c r="O104" s="207"/>
-      <c r="P104" s="207"/>
+      <c r="E99" s="205"/>
+      <c r="F99" s="205"/>
+      <c r="G99" s="205"/>
+      <c r="H99" s="205"/>
+      <c r="I99" s="205"/>
+      <c r="J99" s="205"/>
+      <c r="K99" s="205"/>
+      <c r="L99" s="205"/>
+      <c r="M99" s="205"/>
+      <c r="N99" s="205"/>
+      <c r="O99" s="205"/>
+      <c r="P99" s="205"/>
+    </row>
+    <row r="100" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D100" s="205"/>
+      <c r="E100" s="205"/>
+      <c r="F100" s="205"/>
+      <c r="G100" s="205"/>
+      <c r="H100" s="205"/>
+      <c r="I100" s="205"/>
+      <c r="J100" s="205"/>
+      <c r="K100" s="205"/>
+      <c r="L100" s="205"/>
+      <c r="M100" s="205"/>
+      <c r="N100" s="205"/>
+      <c r="O100" s="205"/>
+      <c r="P100" s="205"/>
+    </row>
+    <row r="101" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D101" s="205"/>
+      <c r="E101" s="205"/>
+      <c r="F101" s="205"/>
+      <c r="G101" s="205"/>
+      <c r="H101" s="205"/>
+      <c r="I101" s="205"/>
+      <c r="J101" s="205"/>
+      <c r="K101" s="205"/>
+      <c r="L101" s="205"/>
+      <c r="M101" s="205"/>
+      <c r="N101" s="205"/>
+      <c r="O101" s="205"/>
+      <c r="P101" s="205"/>
+    </row>
+    <row r="102" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D102" s="205"/>
+      <c r="E102" s="205"/>
+      <c r="F102" s="205"/>
+      <c r="G102" s="205"/>
+      <c r="H102" s="205"/>
+      <c r="I102" s="205"/>
+      <c r="J102" s="205"/>
+      <c r="K102" s="205"/>
+      <c r="L102" s="205"/>
+      <c r="M102" s="205"/>
+      <c r="N102" s="205"/>
+      <c r="O102" s="205"/>
+      <c r="P102" s="205"/>
+    </row>
+    <row r="103" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D103" s="205"/>
+      <c r="E103" s="205"/>
+      <c r="F103" s="205"/>
+      <c r="G103" s="205"/>
+      <c r="H103" s="205"/>
+      <c r="I103" s="205"/>
+      <c r="J103" s="205"/>
+      <c r="K103" s="205"/>
+      <c r="L103" s="205"/>
+      <c r="M103" s="205"/>
+      <c r="N103" s="205"/>
+      <c r="O103" s="205"/>
+      <c r="P103" s="205"/>
+    </row>
+    <row r="104" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D104" s="205"/>
+      <c r="E104" s="205"/>
+      <c r="F104" s="205"/>
+      <c r="G104" s="205"/>
+      <c r="H104" s="205"/>
+      <c r="I104" s="205"/>
+      <c r="J104" s="205"/>
+      <c r="K104" s="205"/>
+      <c r="L104" s="205"/>
+      <c r="M104" s="205"/>
+      <c r="N104" s="205"/>
+      <c r="O104" s="205"/>
+      <c r="P104" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="D94:P95"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="D99:P104"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H3:H4"/>
@@ -9348,14 +9360,14 @@
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="D94:P95"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -9365,19 +9377,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8AEA40-856C-4C69-BDF8-B1FFAA30BA95}">
   <dimension ref="D3:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D3" s="114"/>
     </row>
-    <row r="4" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D4" s="114"/>
     </row>
-    <row r="11" spans="4:10" ht="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:10" ht="67.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D12" s="114"/>
     </row>
-    <row r="13" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D13" s="114"/>
       <c r="E13" s="114"/>
       <c r="F13" s="114"/>
@@ -9386,7 +9398,7 @@
       <c r="I13" s="114"/>
       <c r="J13" s="114"/>
     </row>
-    <row r="14" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D14" s="114"/>
       <c r="E14" s="114"/>
       <c r="F14" s="114"/>
@@ -9395,7 +9407,7 @@
       <c r="I14" s="114"/>
       <c r="J14" s="114"/>
     </row>
-    <row r="15" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D15" s="114"/>
       <c r="E15" s="114"/>
       <c r="F15" s="114"/>
@@ -9404,7 +9416,7 @@
       <c r="I15" s="114"/>
       <c r="J15" s="114"/>
     </row>
-    <row r="16" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E16" s="114"/>
       <c r="F16" s="114"/>
       <c r="G16" s="114"/>
@@ -9412,7 +9424,7 @@
       <c r="I16" s="114"/>
       <c r="J16" s="114"/>
     </row>
-    <row r="17" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E17" s="114"/>
       <c r="F17" s="114"/>
       <c r="G17" s="114"/>
@@ -9420,7 +9432,7 @@
       <c r="I17" s="114"/>
       <c r="J17" s="114"/>
     </row>
-    <row r="18" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D18" s="114"/>
       <c r="E18" s="114"/>
       <c r="F18" s="114"/>
@@ -9429,7 +9441,7 @@
       <c r="I18" s="114"/>
       <c r="J18" s="114"/>
     </row>
-    <row r="21" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D21" s="114"/>
       <c r="E21" s="114"/>
       <c r="F21" s="114"/>
